--- a/logs/Jun_11_full_log/data_corrected.xlsx
+++ b/logs/Jun_11_full_log/data_corrected.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15129\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\logs\Jun_11_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00CF578-448F-4C6A-813A-3752E74D3D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804F7A7E-CC36-43DD-B315-68919F4F8D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,18 @@
     <sheet name="Corrected Data" sheetId="1" r:id="rId1"/>
     <sheet name="QC Summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -6347,7 +6358,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6378,6 +6389,17 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -6425,7 +6447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6450,6 +6472,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6752,7 +6780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB493"/>
+  <dimension ref="A1:AB528"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -49157,6 +49185,266 @@
       <c r="AB493" s="7">
         <v>-52.125634519999998</v>
       </c>
+    </row>
+    <row r="495" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="D495" s="3"/>
+      <c r="E495" s="11"/>
+    </row>
+    <row r="497" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B497" s="3"/>
+      <c r="C497" s="3"/>
+      <c r="D497" s="3"/>
+      <c r="F497" s="10"/>
+      <c r="G497" s="10"/>
+      <c r="H497" s="10"/>
+    </row>
+    <row r="498" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B498" s="3"/>
+      <c r="C498" s="3"/>
+      <c r="D498" s="3"/>
+      <c r="F498" s="10"/>
+      <c r="G498" s="10"/>
+      <c r="H498" s="10"/>
+    </row>
+    <row r="499" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B499" s="3"/>
+      <c r="C499" s="3"/>
+      <c r="D499" s="3"/>
+      <c r="F499" s="10"/>
+      <c r="G499" s="10"/>
+      <c r="H499" s="10"/>
+    </row>
+    <row r="500" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B500" s="3"/>
+      <c r="C500" s="3"/>
+      <c r="D500" s="3"/>
+      <c r="F500" s="10"/>
+      <c r="G500" s="10"/>
+      <c r="H500" s="10"/>
+    </row>
+    <row r="501" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B501" s="3"/>
+      <c r="C501" s="3"/>
+      <c r="D501" s="3"/>
+      <c r="F501" s="10"/>
+      <c r="G501" s="10"/>
+      <c r="H501" s="10"/>
+    </row>
+    <row r="502" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B502" s="3"/>
+      <c r="C502" s="3"/>
+      <c r="D502" s="3"/>
+      <c r="F502" s="10"/>
+      <c r="G502" s="10"/>
+      <c r="H502" s="10"/>
+    </row>
+    <row r="503" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B503" s="3"/>
+      <c r="C503" s="3"/>
+      <c r="D503" s="3"/>
+      <c r="F503" s="10"/>
+      <c r="G503" s="10"/>
+      <c r="H503" s="10"/>
+    </row>
+    <row r="504" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B504" s="3"/>
+      <c r="C504" s="3"/>
+      <c r="D504" s="3"/>
+      <c r="F504" s="10"/>
+      <c r="G504" s="10"/>
+      <c r="H504" s="10"/>
+    </row>
+    <row r="505" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B505" s="3"/>
+      <c r="C505" s="3"/>
+      <c r="D505" s="3"/>
+      <c r="F505" s="10"/>
+      <c r="G505" s="10"/>
+      <c r="H505" s="10"/>
+    </row>
+    <row r="506" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B506" s="3"/>
+      <c r="C506" s="3"/>
+      <c r="D506" s="3"/>
+      <c r="F506" s="10"/>
+      <c r="G506" s="10"/>
+      <c r="H506" s="10"/>
+    </row>
+    <row r="507" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B507" s="3"/>
+      <c r="C507" s="3"/>
+      <c r="D507" s="3"/>
+      <c r="F507" s="10"/>
+      <c r="G507" s="10"/>
+      <c r="H507" s="10"/>
+    </row>
+    <row r="508" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B508" s="3"/>
+      <c r="C508" s="3"/>
+      <c r="D508" s="3"/>
+      <c r="F508" s="10"/>
+      <c r="G508" s="10"/>
+      <c r="H508" s="10"/>
+    </row>
+    <row r="509" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B509" s="3"/>
+      <c r="C509" s="3"/>
+      <c r="D509" s="3"/>
+      <c r="F509" s="10"/>
+      <c r="G509" s="10"/>
+      <c r="H509" s="10"/>
+    </row>
+    <row r="510" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B510" s="3"/>
+      <c r="C510" s="3"/>
+      <c r="D510" s="3"/>
+      <c r="F510" s="10"/>
+      <c r="G510" s="10"/>
+      <c r="H510" s="10"/>
+    </row>
+    <row r="511" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B511" s="3"/>
+      <c r="C511" s="3"/>
+      <c r="D511" s="3"/>
+      <c r="F511" s="10"/>
+      <c r="G511" s="10"/>
+      <c r="H511" s="10"/>
+    </row>
+    <row r="512" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B512" s="3"/>
+      <c r="C512" s="3"/>
+      <c r="D512" s="3"/>
+      <c r="F512" s="10"/>
+      <c r="G512" s="10"/>
+      <c r="H512" s="10"/>
+    </row>
+    <row r="513" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B513" s="3"/>
+      <c r="C513" s="3"/>
+      <c r="D513" s="3"/>
+      <c r="F513" s="10"/>
+      <c r="G513" s="10"/>
+      <c r="H513" s="10"/>
+    </row>
+    <row r="514" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B514" s="3"/>
+      <c r="C514" s="3"/>
+      <c r="D514" s="3"/>
+      <c r="F514" s="10"/>
+      <c r="G514" s="10"/>
+      <c r="H514" s="10"/>
+    </row>
+    <row r="515" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B515" s="3"/>
+      <c r="C515" s="3"/>
+      <c r="D515" s="3"/>
+      <c r="F515" s="10"/>
+      <c r="G515" s="10"/>
+      <c r="H515" s="10"/>
+    </row>
+    <row r="516" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B516" s="3"/>
+      <c r="C516" s="3"/>
+      <c r="D516" s="3"/>
+      <c r="F516" s="10"/>
+      <c r="G516" s="10"/>
+      <c r="H516" s="10"/>
+    </row>
+    <row r="517" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B517" s="3"/>
+      <c r="C517" s="3"/>
+      <c r="D517" s="3"/>
+      <c r="F517" s="10"/>
+      <c r="G517" s="10"/>
+      <c r="H517" s="10"/>
+    </row>
+    <row r="518" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B518" s="3"/>
+      <c r="C518" s="3"/>
+      <c r="D518" s="3"/>
+      <c r="F518" s="10"/>
+      <c r="G518" s="10"/>
+      <c r="H518" s="10"/>
+    </row>
+    <row r="519" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B519" s="3"/>
+      <c r="C519" s="3"/>
+      <c r="D519" s="3"/>
+      <c r="F519" s="10"/>
+      <c r="G519" s="10"/>
+      <c r="H519" s="10"/>
+    </row>
+    <row r="520" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B520" s="3"/>
+      <c r="C520" s="3"/>
+      <c r="D520" s="3"/>
+      <c r="F520" s="10"/>
+      <c r="G520" s="10"/>
+      <c r="H520" s="10"/>
+    </row>
+    <row r="521" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B521" s="3"/>
+      <c r="C521" s="3"/>
+      <c r="D521" s="3"/>
+      <c r="F521" s="10"/>
+      <c r="G521" s="10"/>
+      <c r="H521" s="10"/>
+    </row>
+    <row r="522" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B522" s="3"/>
+      <c r="C522" s="3"/>
+      <c r="D522" s="3"/>
+      <c r="F522" s="10"/>
+      <c r="G522" s="10"/>
+      <c r="H522" s="10"/>
+    </row>
+    <row r="523" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B523" s="3"/>
+      <c r="C523" s="3"/>
+      <c r="D523" s="3"/>
+      <c r="F523" s="10"/>
+      <c r="G523" s="10"/>
+      <c r="H523" s="10"/>
+    </row>
+    <row r="524" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B524" s="3"/>
+      <c r="C524" s="3"/>
+      <c r="D524" s="3"/>
+      <c r="F524" s="10"/>
+      <c r="G524" s="10"/>
+      <c r="H524" s="10"/>
+    </row>
+    <row r="525" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B525" s="3"/>
+      <c r="C525" s="3"/>
+      <c r="D525" s="3"/>
+      <c r="F525" s="10"/>
+      <c r="G525" s="10"/>
+      <c r="H525" s="10"/>
+    </row>
+    <row r="526" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B526" s="3"/>
+      <c r="C526" s="3"/>
+      <c r="D526" s="3"/>
+      <c r="F526" s="3"/>
+      <c r="G526" s="3"/>
+      <c r="H526" s="3"/>
+    </row>
+    <row r="527" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B527" s="3"/>
+      <c r="C527" s="3"/>
+      <c r="D527" s="3"/>
+      <c r="F527" s="3"/>
+      <c r="G527" s="3"/>
+      <c r="H527" s="3"/>
+    </row>
+    <row r="528" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B528" s="3"/>
+      <c r="C528" s="3"/>
+      <c r="D528" s="3"/>
+      <c r="F528" s="3"/>
+      <c r="G528" s="3"/>
+      <c r="H528" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
